--- a/Error Logs/Complete/Fall2024RX_01Yr02_2026.xlsx
+++ b/Error Logs/Complete/Fall2024RX_01Yr02_2026.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://doimspp-my.sharepoint.com/personal/agjohnson_nps_gov1/Documents/Desktop/FFI-QAQC/Error Logs/Complete/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://doimspp-my.sharepoint.com/personal/cfossum_nps_gov1/Documents/Desktop/FFI_QAQC/Error Logs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F7A268D2-65BA-4D0E-BD8F-A148F1E593AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="27" documentId="11_EE62FDCE4D216EA48626533AC33A4F8D7DFA956F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EB4F1EBE-3921-458A-B532-7C4F3CBCE71F}"/>
   <bookViews>
-    <workbookView xWindow="-19310" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="101">
   <si>
     <t>SavedQuery</t>
   </si>
@@ -316,7 +316,13 @@
     <t>false error</t>
   </si>
   <si>
-    <t>false error, DAFR=shrubby cinquefoil</t>
+    <t>false error; need to add to code</t>
+  </si>
+  <si>
+    <t>False Error</t>
+  </si>
+  <si>
+    <t>false error. Code didn't know what to do with decimal. Changed to -3</t>
   </si>
 </sst>
 </file>
@@ -672,6 +678,9 @@
   <dimension ref="A1:E78"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="1" max="1" width="25.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="62.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -738,7 +747,7 @@
         <v>13</v>
       </c>
       <c r="E6" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -969,9 +978,6 @@
       <c r="D26" t="s">
         <v>42</v>
       </c>
-      <c r="E26" t="s">
-        <v>97</v>
-      </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
@@ -1118,7 +1124,7 @@
         <v>55</v>
       </c>
       <c r="E40" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
@@ -1181,9 +1187,6 @@
       </c>
       <c r="D47" t="s">
         <v>62</v>
-      </c>
-      <c r="E47" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
@@ -1549,6 +1552,6 @@
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
-  <clbl:label id="{6dd02d64-b7f3-43f7-a145-cfd68d338edf}" enabled="1" method="Standard" siteId="{0693b5ba-4b18-4d7b-9341-f32f400a5494}" contentBits="0" removed="0"/>
+  <clbl:label id="{6dd02d64-b7f3-43f7-a145-cfd68d338edf}" enabled="1" method="Standard" siteId="{0693b5ba-4b18-4d7b-9341-f32f400a5494}" removed="0"/>
 </clbl:labelList>
 </file>